--- a/src/format.xlsx
+++ b/src/format.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{788D00F5-6AC3-4DD8-94F5-DC654026384C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3F32ED9-D28D-48ED-93F3-152E7FDC2136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Đơn vị / Phân xưởng : </t>
   </si>
   <si>
-    <t>Ca sản xuất:</t>
+    <t>Thời điểm xuất báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">Kỳ báo cáo : </t>
@@ -431,113 +431,113 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,93 +867,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="22"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="22.5">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="25"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="26"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="14" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="28"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="14" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="14" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="28"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="25"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="26"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -974,22 +974,22 @@
       <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="31"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="32"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="33"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -998,10 +998,10 @@
         <v>20</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="34"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="35"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1010,114 +1010,114 @@
         <v>20</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="33"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="34"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="35"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="33"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="34"/>
+      <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="35"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="33"/>
+      <c r="A16" s="20"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="34"/>
+      <c r="H16" s="21"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="35"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="36"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="33"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="34"/>
+      <c r="H18" s="21"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="35"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="36"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="33"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="34"/>
+      <c r="H20" s="21"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="35"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="36"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="7">
         <f>SUM(D9:D21)</f>
         <v>0</v>
@@ -1130,78 +1130,73 @@
         <f>AVERAGE(F9:F21)</f>
         <v>20</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="38"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="39"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="40"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="25"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="40"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="25"/>
     </row>
     <row r="25" spans="1:8" ht="21" customHeight="1">
-      <c r="A25" s="42"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="43"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
     </row>
     <row r="26" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A26" s="42"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="43"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
     </row>
     <row r="27" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A27" s="42"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="43"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1">
-      <c r="A28" s="42"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="43"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="F6:H6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="A23:C23"/>
@@ -1215,6 +1210,11 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="F6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
